--- a/uploads/subject_requirements.xlsx
+++ b/uploads/subject_requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NITRO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F399CA9E-A21C-4ABD-9240-E279CE364F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071F1BFA-B7A4-4E93-9BAC-911A275EDDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23619E72-95E4-42DE-AF46-1D3CB9C6EB71}"/>
+    <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8880" xr2:uid="{23619E72-95E4-42DE-AF46-1D3CB9C6EB71}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="46">
   <si>
     <t>class</t>
   </si>
@@ -111,9 +111,6 @@
     <t>LT</t>
   </si>
   <si>
-    <t>CP/IT W/S</t>
-  </si>
-  <si>
     <t>S2_CSE_A</t>
   </si>
   <si>
@@ -166,6 +163,15 @@
   </si>
   <si>
     <t>BCT/IOT</t>
+  </si>
+  <si>
+    <t>CP lab/IT W/S</t>
+  </si>
+  <si>
+    <t>CP LAB/IT W/S</t>
+  </si>
+  <si>
+    <t>CP /ITLAB W/S</t>
   </si>
 </sst>
 </file>
@@ -232,9 +238,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -272,7 +278,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -378,7 +384,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -520,7 +526,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -749,7 +755,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -763,7 +769,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
         <v>16</v>
@@ -777,7 +783,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>17</v>
@@ -791,7 +797,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
         <v>18</v>
@@ -805,7 +811,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>19</v>
@@ -819,7 +825,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
@@ -833,7 +839,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
@@ -847,7 +853,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>22</v>
@@ -861,7 +867,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -875,7 +881,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
@@ -889,10 +895,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -903,7 +909,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -917,7 +923,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
@@ -931,7 +937,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
@@ -945,7 +951,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
         <v>18</v>
@@ -959,7 +965,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
         <v>19</v>
@@ -973,7 +979,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
@@ -987,7 +993,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
         <v>21</v>
@@ -1001,7 +1007,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
         <v>22</v>
@@ -1015,7 +1021,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -1029,7 +1035,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
         <v>24</v>
@@ -1043,10 +1049,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1057,10 +1063,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -1071,10 +1077,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>27</v>
+      </c>
+      <c r="B39" t="s">
         <v>28</v>
-      </c>
-      <c r="B39" t="s">
-        <v>29</v>
       </c>
       <c r="C39">
         <v>6</v>
@@ -1085,10 +1091,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -1099,10 +1105,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -1113,10 +1119,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -1127,10 +1133,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -1141,10 +1147,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C44">
         <v>6</v>
@@ -1155,10 +1161,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -1169,10 +1175,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46">
         <v>6</v>
@@ -1183,10 +1189,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47">
         <v>6</v>
@@ -1197,10 +1203,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C48">
         <v>6</v>
@@ -1211,10 +1217,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C49">
         <v>5</v>
@@ -1225,10 +1231,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -1239,10 +1245,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C51">
         <v>6</v>
@@ -1253,10 +1259,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s">
         <v>37</v>
-      </c>
-      <c r="B52" t="s">
-        <v>38</v>
       </c>
       <c r="C52">
         <v>5</v>
@@ -1267,10 +1273,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1281,10 +1287,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C54">
         <v>5</v>
@@ -1295,10 +1301,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -1309,10 +1315,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C56">
         <v>14</v>
@@ -1323,10 +1329,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C57">
         <v>5</v>

--- a/uploads/subject_requirements.xlsx
+++ b/uploads/subject_requirements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071F1BFA-B7A4-4E93-9BAC-911A275EDDDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A95B3BA-4FBE-4C17-B9D3-22821F223105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2544" yWindow="2544" windowWidth="17280" windowHeight="8880" xr2:uid="{23619E72-95E4-42DE-AF46-1D3CB9C6EB71}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="47">
   <si>
     <t>class</t>
   </si>
@@ -159,19 +159,22 @@
     <t>PROJECT</t>
   </si>
   <si>
-    <t>CSA/DM</t>
-  </si>
-  <si>
-    <t>BCT/IOT</t>
-  </si>
-  <si>
-    <t>CP lab/IT W/S</t>
-  </si>
-  <si>
     <t>CP LAB/IT W/S</t>
   </si>
   <si>
     <t>CP /ITLAB W/S</t>
+  </si>
+  <si>
+    <t>BCT</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>CSA</t>
+  </si>
+  <si>
+    <t>DM</t>
   </si>
 </sst>
 </file>
@@ -534,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2AC3A33-A8CD-4725-822E-EC12DE8C587F}">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" customWidth="1"/>
@@ -898,7 +901,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1052,7 +1055,7 @@
         <v>26</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1304,7 +1307,7 @@
         <v>36</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -1318,13 +1321,13 @@
         <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C56">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1332,12 +1335,37 @@
         <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58">
+        <v>5</v>
+      </c>
+      <c r="D58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
         <v>5</v>
       </c>
     </row>
